--- a/day10/matrix.xlsx
+++ b/day10/matrix.xlsx
@@ -425,308 +425,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SRNO</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SRNO</t>
+          <t xml:space="preserve">BRANCH </t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRANCH </t>
+          <t>NAME</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>NAME</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>PERCENTAGE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>PERCENTAGE</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>PASSFAIL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KATHAN</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>285</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>JATAN</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>270</v>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>KATHAN</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>285</v>
-      </c>
-      <c r="F2" t="n">
-        <v>95</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MAHESH</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RAMESH</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>210</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NAYAN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>195</v>
+      </c>
+      <c r="E6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NARESH</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>180</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RAMAN</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>165</v>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>CE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JATAN</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>270</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SURESH</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RATAN</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>150</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JAYESH</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>90</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MAHESH</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>225</v>
-      </c>
-      <c r="F4" t="n">
-        <v>75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RAMESH</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>210</v>
-      </c>
-      <c r="F5" t="n">
-        <v>70</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NAYAN</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>195</v>
-      </c>
-      <c r="F6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NARESH</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>180</v>
-      </c>
-      <c r="F7" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RAMAN</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>165</v>
-      </c>
-      <c r="F8" t="n">
-        <v>55</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SURESH</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>150</v>
-      </c>
-      <c r="F9" t="n">
-        <v>50</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RATAN</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>150</v>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>JAYESH</t>
-        </is>
-      </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
-      </c>
-      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
